--- a/libertadores/datasets_liberta/times_3o_lugar_fase_1.xlsx
+++ b/libertadores/datasets_liberta/times_3o_lugar_fase_1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>Origem</t>
   </si>
@@ -22,6 +22,9 @@
     <t>Grupo</t>
   </si>
   <si>
+    <t>ID do Time</t>
+  </si>
+  <si>
     <t>Nome do Time</t>
   </si>
   <si>
@@ -76,25 +79,25 @@
     <t>JUV. KP</t>
   </si>
   <si>
-    <t>S.E.R. GRILLO</t>
+    <t>Máquina Laranjja</t>
   </si>
   <si>
     <t>dasdoresfc</t>
   </si>
   <si>
-    <t>Mau Humor F.C.</t>
+    <t>Grêmio imortal 36</t>
   </si>
   <si>
     <t>FÚRIA LEON</t>
   </si>
   <si>
-    <t>DM Studio</t>
+    <t>AZURRA82</t>
   </si>
   <si>
     <t>Grêmio imortal 37</t>
   </si>
   <si>
-    <t>Texas Club 2026</t>
+    <t>Super Vasco f.c</t>
   </si>
 </sst>
 </file>
@@ -452,10 +455,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,261 +489,288 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>13951133</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>397.31982421875</v>
+      </c>
+      <c r="J2">
+        <v>421.3701171875</v>
+      </c>
+      <c r="K2">
+        <v>-24.05029296875</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>30267301</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>434.969970703125</v>
+      </c>
+      <c r="J3">
+        <v>476.159423828125</v>
+      </c>
+      <c r="K3">
+        <v>-41.189453125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>7017989</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>444.58935546875</v>
+      </c>
+      <c r="J4">
+        <v>484.069580078125</v>
+      </c>
+      <c r="K4">
+        <v>-39.480224609375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>24856400</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>435.2802734375</v>
+      </c>
+      <c r="J5">
+        <v>469.849609375</v>
+      </c>
+      <c r="K5">
+        <v>-34.5693359375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>18344271</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>449.610107421875</v>
+      </c>
+      <c r="J6">
+        <v>434.02001953125</v>
+      </c>
+      <c r="K6">
+        <v>15.590087890625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>18346776</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>9</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
+        <v>424.860107421875</v>
+      </c>
+      <c r="J7">
+        <v>396.5498046875</v>
+      </c>
+      <c r="K7">
+        <v>28.310302734375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>24468241</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>456.26025390625</v>
+      </c>
+      <c r="J8">
+        <v>457.349609375</v>
+      </c>
+      <c r="K8">
+        <v>-1.08935546875</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="D2">
-        <v>6</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>343.10986328125</v>
-      </c>
-      <c r="I2">
-        <v>358.4501953125</v>
-      </c>
-      <c r="J2">
-        <v>-15.34033203125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>361.580078125</v>
-      </c>
-      <c r="I3">
-        <v>371.899658203125</v>
-      </c>
-      <c r="J3">
-        <v>-10.319580078125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>377.9794921875</v>
-      </c>
-      <c r="I4">
-        <v>427.669677734375</v>
-      </c>
-      <c r="J4">
-        <v>-49.690185546875</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>385.189453125</v>
-      </c>
-      <c r="I5">
-        <v>361.5703125</v>
-      </c>
-      <c r="J5">
-        <v>23.619140625</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>376.389892578125</v>
-      </c>
-      <c r="I6">
-        <v>368.1298828125</v>
-      </c>
-      <c r="J6">
-        <v>8.260009765625</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>368.849853515625</v>
-      </c>
-      <c r="I7">
-        <v>386.490234375</v>
-      </c>
-      <c r="J7">
-        <v>-17.640380859375</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8">
-        <v>6</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-      <c r="H8">
-        <v>394.16015625</v>
-      </c>
-      <c r="I8">
-        <v>387.9296875</v>
-      </c>
-      <c r="J8">
-        <v>6.23046875</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9">
-        <v>6</v>
+      <c r="C9">
+        <v>13707047</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>414.169921875</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>414.89990234375</v>
+        <v>470.1796875</v>
       </c>
       <c r="J9">
-        <v>-0.72998046875</v>
+        <v>468.0693359375</v>
+      </c>
+      <c r="K9">
+        <v>2.1103515625</v>
       </c>
     </row>
   </sheetData>
